--- a/ENDERECOS-ROTA.xlsx
+++ b/ENDERECOS-ROTA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,7 +43,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,57 +436,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Numero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Bairro</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cep</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Destinatário</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Endereco</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Origem_Geo</t>
         </is>
@@ -522,10 +534,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-22.0856768</v>
+        <v>-22.084585</v>
       </c>
       <c r="J2" t="n">
-        <v>-48.7526652</v>
+        <v>-48.7532208</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -631,7 +643,7 @@
         <v>-22.0815719</v>
       </c>
       <c r="J4" t="n">
-        <v>-48.7476383</v>
+        <v>-48.7476382</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1064,49 +1076,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MARCELA FERNANDA FAXINA DOS SANTOS </t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Rua João Francisco Pizato</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Parque Residencial Vila Rica</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Dois Córregos</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>17300188</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MARCELA FERNANDA FAXINA DOS SANTOS </t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Rua João Francisco Pizzato, 110, Parque Residencial Vila Rica, Dois Córregos - SP</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Nao_Encontrado</t>
         </is>

--- a/ENDERECOS-ROTA.xlsx
+++ b/ENDERECOS-ROTA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,7 +40,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,57 +424,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Numero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Bairro</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cep</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Destinatário</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Endereco</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Origem_Geo</t>
         </is>
@@ -534,10 +522,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-22.084585</v>
+        <v>-22.0856768</v>
       </c>
       <c r="J2" t="n">
-        <v>-48.7532208</v>
+        <v>-48.7526652</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -643,7 +631,7 @@
         <v>-22.0815719</v>
       </c>
       <c r="J4" t="n">
-        <v>-48.7476382</v>
+        <v>-48.7476383</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1076,49 +1064,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">MARCELA FERNANDA FAXINA DOS SANTOS </t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Rua João Francisco Pizato</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>Parque Residencial Vila Rica</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Dois Córregos</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>17300188</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">MARCELA FERNANDA FAXINA DOS SANTOS </t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>Rua João Francisco Pizzato, 110, Parque Residencial Vila Rica, Dois Córregos - SP</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>Nao_Encontrado</t>
         </is>

--- a/ENDERECOS-ROTA.xlsx
+++ b/ENDERECOS-ROTA.xlsx
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-22.084585</v>
+        <v>-22.0884218</v>
       </c>
       <c r="J2" t="n">
-        <v>-48.7532208</v>
+        <v>-48.7510661</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-22.0867376</v>
+        <v>-22.0907603</v>
       </c>
       <c r="J6" t="n">
-        <v>-48.7506314</v>
+        <v>-48.7483911</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
